--- a/reports/pdf_rolling5_20260708.xlsx
+++ b/reports/pdf_rolling5_20260708.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,102억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 13종목  /  매도 16종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,034억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 13종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>145</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1715661750</v>
+        <v>1717272700</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1102594500</v>
+        <v>-1103629800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2773260000</v>
+        <v>2775864000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-49</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2817990000</v>
+        <v>-2820636000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2032020000</v>
+        <v>2033928000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-37</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1306275750</v>
+        <v>-1307502300</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>33</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1309151250</v>
+        <v>1310380500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-36</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1023678000</v>
+        <v>-1024639200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>476736600</v>
+        <v>477184240</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-509922000</v>
+        <v>-510400800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1402392000</v>
+        <v>1403708800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-5008162500</v>
+        <v>-5012865000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>526003500</v>
+        <v>526497400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-24</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2157264000</v>
+        <v>-2159289600</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>470730000</v>
+        <v>1360216000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.36%</t>
+          <t>3.38%→3.57%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>116→126</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -999,7 +999,7 @@
         <v>-20</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2198160000</v>
+        <v>-2200224000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1015,23 +1015,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1358940000</v>
+        <v>471172000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.38%→3.57%</t>
+          <t>0.20%→0.36%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>116→126</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>-19</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1770562500</v>
+        <v>-1772225000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1096524000</v>
+        <v>1097553600</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-17</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-993964500</v>
+        <v>-994897800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>433242000</v>
+        <v>433648800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-13</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-948382500</v>
+        <v>-949273000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>454222500</v>
+        <v>454649000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1320280500</v>
+        <v>-1321520200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1437750000</v>
+        <v>1439100000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1378536000</v>
+        <v>-1379830400</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>-7</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1015371000</v>
+        <v>-1016324400</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-3041640000</v>
+        <v>-3044496000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>-3</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-746032500</v>
+        <v>-746733000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,517억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,657억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1415,7 +1415,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>414419200</v>
+        <v>415126400</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>-20</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1578684000</v>
+        <v>-1581378000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>1511880000</v>
+        <v>1514460000</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,251억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 2종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,176억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 2종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1576,7 +1576,7 @@
         <v>221</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>7979569650</v>
+        <v>8030786400</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>-56</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-6325480000</v>
+        <v>-6366080000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>7957485000</v>
+        <v>8008560000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>-49</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1421869750</v>
+        <v>-1430996000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>-36</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-3160558800</v>
+        <v>-3180844800</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>-20</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2181200000</v>
+        <v>-2195200000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,694억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,760억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1737,7 +1737,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 356억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 17종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 17종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1833,11 +1833,11 @@
         <v>91</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>24214190</v>
+        <v>23390640</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.39%→0.46%</t>
+          <t>0.38%→0.45%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1854,11 +1854,11 @@
         <v>-318</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-105738180</v>
+        <v>-105245280</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2.93%→2.62%</t>
+          <t>2.96%→2.64%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1877,11 +1877,11 @@
         <v>37</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>99060100</v>
+        <v>102408600</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.29%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1898,7 +1898,7 @@
         <v>-268</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-149656560</v>
+        <v>-147228480</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1921,11 +1921,11 @@
         <v>23</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>302514400</v>
+        <v>280140000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.47%→3.33%</t>
+          <t>2.32%→3.13%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1942,11 +1942,11 @@
         <v>-76</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-152684000</v>
+        <v>-130872000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.55%→3.10%</t>
+          <t>3.08%→2.70%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1965,11 +1965,11 @@
         <v>23</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>92508300</v>
+        <v>89161800</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.82%</t>
+          <t>1.52%→1.78%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1986,11 +1986,11 @@
         <v>-63</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-98463960</v>
+        <v>-97584480</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.20%</t>
+          <t>0.49%→0.20%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2009,11 +2009,11 @@
         <v>18</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>143614800</v>
+        <v>131846400</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.46%→3.86%</t>
+          <t>3.22%→3.59%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2030,11 +2030,11 @@
         <v>-48</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-135988800</v>
+        <v>-142329600</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>6.19%→5.77%</t>
+          <t>6.56%→6.13%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2053,11 +2053,11 @@
         <v>17</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>173553000</v>
+        <v>160935600</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.50%</t>
+          <t>1.88%→2.35%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2074,11 +2074,11 @@
         <v>-26</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-100097400</v>
+        <v>-99918000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>7.29%→6.97%</t>
+          <t>7.37%→7.06%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2097,11 +2097,11 @@
         <v>12</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>54218400</v>
+        <v>52113600</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.56%→0.72%</t>
+          <t>0.55%→0.70%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2111,23 +2111,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-41442800</v>
+        <v>-54507600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.59%</t>
+          <t>2.39%→2.23%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>83→69</t>
+          <t>210→196</t>
         </is>
       </c>
     </row>
@@ -2141,11 +2141,11 @@
         <v>11</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>19167500</v>
+        <v>17925600</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.39%→0.44%</t>
+          <t>0.37%→0.42%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-55391000</v>
+        <v>-40983600</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.23%</t>
+          <t>0.71%→0.59%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>210→196</t>
+          <t>83→69</t>
         </is>
       </c>
     </row>
@@ -2185,11 +2185,11 @@
         <v>10</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>63632000</v>
+        <v>60900000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.78%</t>
+          <t>2.53%→2.70%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2206,11 +2206,11 @@
         <v>-13</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-113848800</v>
+        <v>-112694400</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.48%→2.14%</t>
+          <t>2.49%→2.15%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2229,11 +2229,11 @@
         <v>9</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>112692600</v>
+        <v>113475600</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.41%→1.73%</t>
+          <t>1.44%→1.77%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2250,11 +2250,11 @@
         <v>-13</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-39442000</v>
+        <v>-36254400</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.24%</t>
+          <t>0.33%→0.22%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2273,11 +2273,11 @@
         <v>8</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>112044800</v>
+        <v>108729600</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.74%</t>
+          <t>2.39%→2.70%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2294,11 +2294,11 @@
         <v>-10</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-62238000</v>
+        <v>-71652000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.86%→0.68%</t>
+          <t>1.01%→0.80%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2310,23 +2310,23 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>40344000</v>
+        <v>41076000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.01%</t>
+          <t>1.46%→1.58%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>73→79</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -2338,11 +2338,11 @@
         <v>-9</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-57195000</v>
+        <v>-62294400</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.40%</t>
+          <t>2.84%→2.65%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2354,23 +2354,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>42115200</v>
+        <v>70560000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>1.48%→1.60%</t>
+          <t>1.24%→1.44%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>73→79</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2382,11 +2382,11 @@
         <v>-8</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-178432000</v>
+        <v>-182112000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2.06%→1.54%</t>
+          <t>2.13%→1.60%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2398,23 +2398,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>74538000</v>
+        <v>38656800</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.50%</t>
+          <t>0.87%→0.98%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2426,11 +2426,11 @@
         <v>-7</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-73012800</v>
+        <v>-75028800</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.23%→3.00%</t>
+          <t>3.36%→3.13%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2449,11 +2449,11 @@
         <v>5</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>20151500</v>
+        <v>18732000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.24%</t>
+          <t>1.12%→1.17%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2470,11 +2470,11 @@
         <v>-4</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-38868000</v>
+        <v>-36422400</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.16%→2.04%</t>
+          <t>2.05%→1.94%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2493,11 +2493,11 @@
         <v>4</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>103156000</v>
+        <v>102984000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>1.64%→1.93%</t>
+          <t>1.66%→1.95%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2521,11 +2521,11 @@
         <v>3</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>58794000</v>
+        <v>58086000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.65%</t>
+          <t>2.49%→2.66%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2542,7 +2542,7 @@
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 6종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B61" s="4" t="n"/>
@@ -2638,11 +2638,11 @@
         <v>297</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>878273550</v>
+        <v>974278800</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.49%</t>
+          <t>0.00%→1.61%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2659,7 +2659,7 @@
         <v>-685</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-842049950</v>
+        <v>-834973900</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2682,11 +2682,11 @@
         <v>77</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>156412410</v>
+        <v>146829760</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>1.56%→2.09%</t>
+          <t>1.56%→1.91%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2703,11 +2703,11 @@
         <v>-122</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-1959930000</v>
+        <v>-1939141200</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>13.07%→9.24%</t>
+          <t>13.07%→8.93%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2726,11 +2726,11 @@
         <v>35</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>732623500</v>
+        <v>735966000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>4.79%→6.62%</t>
+          <t>4.79%→6.50%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2747,11 +2747,11 @@
         <v>-36</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-547495200</v>
+        <v>-578577600</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>10.76%→9.23%</t>
+          <t>10.76%→9.54%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2770,11 +2770,11 @@
         <v>16</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>805392000</v>
+        <v>811840000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>4.26%→6.39%</t>
+          <t>4.26%→6.29%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2791,11 +2791,11 @@
         <v>-13</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-512057000</v>
+        <v>-517725000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>10.30%→9.59%</t>
+          <t>10.30%→9.48%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2814,11 +2814,11 @@
         <v>14</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>523124000</v>
+        <v>562506000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>2.11%→2.91%</t>
+          <t>2.11%→3.05%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2842,11 +2842,11 @@
         <v>4</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>42935200</v>
+        <v>44320800</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>7.40%→7.50%</t>
+          <t>7.40%→7.56%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">

--- a/reports/pdf_rolling5_20260708.xlsx
+++ b/reports/pdf_rolling5_20260708.xlsx
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1360216000</v>
+        <v>471172000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.38%→3.57%</t>
+          <t>0.20%→0.36%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>116→126</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1015,23 +1015,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>471172000</v>
+        <v>1360216000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.36%</t>
+          <t>3.38%→3.57%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>116→126</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1914,23 +1914,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>280140000</v>
+        <v>89161800</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.32%→3.13%</t>
+          <t>1.52%→1.78%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>65→88</t>
+          <t>134→157</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -1958,23 +1958,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>23</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>89161800</v>
+        <v>280140000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>1.52%→1.78%</t>
+          <t>2.32%→3.13%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>134→157</t>
+          <t>65→88</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -2354,23 +2354,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>70560000</v>
+        <v>38656800</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>1.24%→1.44%</t>
+          <t>0.87%→0.98%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>46→52</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2398,23 +2398,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>38656800</v>
+        <v>70560000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>0.87%→0.98%</t>
+          <t>1.24%→1.44%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>46→52</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260708.xlsx
+++ b/reports/pdf_rolling5_20260708.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-01 ~ 2026-07-08  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-01 ~ 2026-07-08  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1024639200</v>
+        <v>-510400800</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.76%→0.57%</t>
+          <t>0.48%→0.52%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>133→97</t>
+          <t>213→177</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-510400800</v>
+        <v>-1024639200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.52%</t>
+          <t>0.76%→0.57%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>213→177</t>
+          <t>133→97</t>
         </is>
       </c>
     </row>
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>471172000</v>
+        <v>1360216000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.36%</t>
+          <t>3.38%→3.57%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>116→126</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1015,23 +1015,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1360216000</v>
+        <v>471172000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.38%→3.57%</t>
+          <t>0.20%→0.36%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>116→126</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1735,1170 +1735,380 @@
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 17종목  /  매도 15종목</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 6종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>에이프로</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>23390640</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>0.38%→0.45%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>510→601</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-318</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-105245280</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>2.96%→2.64%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>3,054→2,736</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크  (신규)</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>102408600</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.30%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>0→37</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>LS증권</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-268</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-147228480</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>0.73%→0.30%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>452→184</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>큐리오시스  (신규)</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>23</v>
+        <v>297</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>89161800</v>
+        <v>974278800</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.52%→1.78%</t>
+          <t>0.00%→1.61%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>134→157</t>
+          <t>0→297</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>지아이이노베이션  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-76</v>
+        <v>-685</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-130872000</v>
+        <v>-834973900</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.08%→2.70%</t>
+          <t>1.29%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>612→536</t>
+          <t>685→0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>280140000</v>
+        <v>146829760</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.32%→3.13%</t>
+          <t>1.56%→1.91%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>65→88</t>
+          <t>530→607</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>다우데이타</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-63</v>
+        <v>-122</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-97584480</v>
+        <v>-1939141200</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.20%</t>
+          <t>13.07%→8.93%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>107→44</t>
+          <t>462→340</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>131846400</v>
+        <v>735966000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.22%→3.59%</t>
+          <t>4.79%→6.50%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>150→168</t>
+          <t>152→187</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-48</v>
+        <v>-36</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-142329600</v>
+        <v>-578577600</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>6.56%→6.13%</t>
+          <t>10.76%→9.54%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>756→708</t>
+          <t>395→359</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>160935600</v>
+        <v>811840000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.88%→2.35%</t>
+          <t>4.26%→6.29%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>68→85</t>
+          <t>59→75</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-26</v>
+        <v>-13</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-99918000</v>
+        <v>-517725000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>7.37%→7.06%</t>
+          <t>10.30%→9.48%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>655→629</t>
+          <t>157→144</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>52113600</v>
+        <v>562506000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.55%→0.70%</t>
+          <t>2.11%→3.05%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>43→55</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-54507600</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>2.39%→2.23%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>210→196</t>
-        </is>
-      </c>
+          <t>32→46</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>17925600</v>
+        <v>44320800</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.37%→0.42%</t>
+          <t>7.40%→7.56%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>77→88</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>솔브레인홀딩스</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-40983600</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>0.71%→0.59%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>83→69</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>코미코</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>60900000</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>2.53%→2.70%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>142→152</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>두산테스나</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-112694400</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>2.49%→2.15%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>98→85</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>ISC</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>113475600</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.44%→1.77%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>39→48</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>삼현</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-36254400</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>0.33%→0.22%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>40→27</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>108729600</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>2.39%→2.70%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>60→68</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-71652000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>1.01%→0.80%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>48→38</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>대주전자재료</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>41076000</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>1.46%→1.58%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>73→79</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-62294400</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>2.84%→2.65%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>140→131</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>씨엠티엑스</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>38656800</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>0.87%→0.98%</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>46→52</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>파크시스템스</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-182112000</v>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>2.13%→1.60%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>32→24</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>70560000</v>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>1.24%→1.44%</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>36→42</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>-75028800</v>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>3.36%→3.13%</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>107→100</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C57" s="11" t="n">
-        <v>18732000</v>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>1.12%→1.17%</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>102→107</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>심텍</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I57" s="15" t="n">
-        <v>-36422400</v>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>2.05%→1.94%</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>77→73</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>솔브레인</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>102984000</v>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>1.66%→1.95%</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>22→26</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="n"/>
-      <c r="H58" s="17" t="n"/>
-      <c r="I58" s="17" t="n"/>
-      <c r="J58" s="17" t="n"/>
-      <c r="K58" s="17" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C59" s="11" t="n">
-        <v>58086000</v>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>2.49%→2.66%</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>44→47</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="17" t="n"/>
-      <c r="J59" s="17" t="n"/>
-      <c r="K59" s="17" t="n"/>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 6종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>큐리오시스  (신규)</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="n">
-        <v>297</v>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>974278800</v>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.61%</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>0→297</t>
-        </is>
-      </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>지아이이노베이션  (편출)</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="n">
-        <v>-685</v>
-      </c>
-      <c r="I64" s="15" t="n">
-        <v>-834973900</v>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>1.29%→0.00%</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
-        <is>
-          <t>685→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>리센스메디컬</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>146829760</v>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>1.56%→1.91%</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>530→607</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="n">
-        <v>-122</v>
-      </c>
-      <c r="I65" s="15" t="n">
-        <v>-1939141200</v>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>13.07%→8.93%</t>
-        </is>
-      </c>
-      <c r="K65" s="13" t="inlineStr">
-        <is>
-          <t>462→340</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>735966000</v>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t>4.79%→6.50%</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>152→187</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <v>-578577600</v>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>10.76%→9.54%</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>395→359</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>한미약품</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>811840000</v>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>4.26%→6.29%</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>59→75</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <v>-517725000</v>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>10.30%→9.48%</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>157→144</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C68" s="11" t="n">
-        <v>562506000</v>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>2.11%→3.05%</t>
-        </is>
-      </c>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>32→46</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="n"/>
-      <c r="H68" s="17" t="n"/>
-      <c r="I68" s="17" t="n"/>
-      <c r="J68" s="17" t="n"/>
-      <c r="K68" s="17" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>에이비엘바이오</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C69" s="11" t="n">
-        <v>44320800</v>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>7.40%→7.56%</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
           <t>409→413</t>
         </is>
       </c>
-      <c r="G69" s="17" t="n"/>
-      <c r="H69" s="17" t="n"/>
-      <c r="I69" s="17" t="n"/>
-      <c r="J69" s="17" t="n"/>
-      <c r="K69" s="17" t="n"/>
-    </row>
-    <row r="71" ht="19" customHeight="1">
-      <c r="A71" s="19" t="inlineStr">
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n"/>
-      <c r="C71" s="20" t="n"/>
-      <c r="D71" s="20" t="n"/>
-      <c r="E71" s="20" t="n"/>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n"/>
-      <c r="H71" s="20" t="n"/>
-      <c r="I71" s="20" t="n"/>
-      <c r="J71" s="20" t="n"/>
-      <c r="K71" s="20" t="n"/>
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20" t="n"/>
+      <c r="I52" s="20" t="n"/>
+      <c r="J52" s="20" t="n"/>
+      <c r="K52" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="18">
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="G43:K43"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="G62:K62"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="G30:K30"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A71:K71"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260708.xlsx
+++ b/reports/pdf_rolling5_20260708.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-01 ~ 2026-07-08  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-01 ~ 2026-07-08  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-510400800</v>
+        <v>-1024639200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.52%</t>
+          <t>0.76%→0.57%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>213→177</t>
+          <t>133→97</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1024639200</v>
+        <v>-510400800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.76%→0.57%</t>
+          <t>0.48%→0.52%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>133→97</t>
+          <t>213→177</t>
         </is>
       </c>
     </row>
@@ -1735,380 +1735,1170 @@
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n"/>
-      <c r="C40" s="20" t="n"/>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="20" t="n"/>
-      <c r="H40" s="20" t="n"/>
-      <c r="I40" s="20" t="n"/>
-      <c r="J40" s="20" t="n"/>
-      <c r="K40" s="20" t="n"/>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 6종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 343억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 17종목  /  매도 15종목</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>23390640</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>0.38%→0.45%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>510→601</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-318</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-105245280</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>2.96%→2.64%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>3,054→2,736</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K44" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>네패스아크  (신규)</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>102408600</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.30%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>0→37</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>LS증권</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-268</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-147228480</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.30%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>452→184</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>큐리오시스  (신규)</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>974278800</v>
+        <v>89161800</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.61%</t>
+          <t>1.52%→1.78%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>0→297</t>
+          <t>134→157</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>지아이이노베이션  (편출)</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-685</v>
+        <v>-76</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-834973900</v>
+        <v>-130872000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>1.29%→0.00%</t>
+          <t>3.08%→2.70%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>685→0</t>
+          <t>612→536</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>146829760</v>
+        <v>280140000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.91%</t>
+          <t>2.32%→3.13%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>530→607</t>
+          <t>65→88</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>다우데이타</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-122</v>
+        <v>-63</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1939141200</v>
+        <v>-97584480</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>13.07%→8.93%</t>
+          <t>0.49%→0.20%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>462→340</t>
+          <t>107→44</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>735966000</v>
+        <v>131846400</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>4.79%→6.50%</t>
+          <t>3.22%→3.59%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>152→187</t>
+          <t>150→168</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-36</v>
+        <v>-48</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-578577600</v>
+        <v>-142329600</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>10.76%→9.54%</t>
+          <t>6.56%→6.13%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>395→359</t>
+          <t>756→708</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>811840000</v>
+        <v>160935600</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>4.26%→6.29%</t>
+          <t>1.88%→2.35%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>59→75</t>
+          <t>68→85</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-13</v>
+        <v>-26</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-517725000</v>
+        <v>-99918000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>10.30%→9.48%</t>
+          <t>7.37%→7.06%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>157→144</t>
+          <t>655→629</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>562506000</v>
+        <v>52113600</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.11%→3.05%</t>
+          <t>0.55%→0.70%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>32→46</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="17" t="n"/>
-      <c r="J49" s="17" t="n"/>
-      <c r="K49" s="17" t="n"/>
+          <t>43→55</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-54507600</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>2.39%→2.23%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>210→196</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>17925600</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>0.37%→0.42%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>77→88</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-40983600</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.59%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>83→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>60900000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2.53%→2.70%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>142→152</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-112694400</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>2.49%→2.15%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>98→85</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>113475600</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.44%→1.77%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>39→48</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>삼현</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-36254400</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.33%→0.22%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>40→27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>108729600</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>2.39%→2.70%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>60→68</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-71652000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>1.01%→0.80%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>48→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>70560000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>1.24%→1.44%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>36→42</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-62294400</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>2.84%→2.65%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>140→131</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>38656800</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>0.87%→0.98%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>46→52</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-182112000</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>2.13%→1.60%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>32→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>41076000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>1.46%→1.58%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>73→79</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-75028800</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>3.36%→3.13%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>107→100</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>18732000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>1.12%→1.17%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-36422400</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>2.05%→1.94%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>77→73</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>솔브레인</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>102984000</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>1.66%→1.95%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>22→26</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="n"/>
+      <c r="H58" s="17" t="n"/>
+      <c r="I58" s="17" t="n"/>
+      <c r="J58" s="17" t="n"/>
+      <c r="K58" s="17" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>58086000</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>2.49%→2.66%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>44→47</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="n"/>
+      <c r="H59" s="17" t="n"/>
+      <c r="I59" s="17" t="n"/>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 614억      오늘 2026-07-08  vs  5일전 2026-07-01      매수 6종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>큐리오시스  (신규)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>297</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>974278800</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.61%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>0→297</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션  (편출)</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-685</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-834973900</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>1.29%→0.00%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>685→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>리센스메디컬</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>146829760</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>1.56%→1.91%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>530→607</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-1939141200</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>13.07%→8.93%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>462→340</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>735966000</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>4.79%→6.50%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>152→187</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-578577600</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>10.76%→9.54%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>395→359</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>811840000</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>4.26%→6.29%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>59→75</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-517725000</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>10.30%→9.48%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>157→144</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>562506000</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>2.11%→3.05%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>32→46</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="n"/>
+      <c r="H68" s="17" t="n"/>
+      <c r="I68" s="17" t="n"/>
+      <c r="J68" s="17" t="n"/>
+      <c r="K68" s="17" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="B50" s="11" t="n">
+      <c r="B69" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="11" t="n">
+      <c r="C69" s="11" t="n">
         <v>44320800</v>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>7.40%→7.56%</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>409→413</t>
         </is>
       </c>
-      <c r="G50" s="17" t="n"/>
-      <c r="H50" s="17" t="n"/>
-      <c r="I50" s="17" t="n"/>
-      <c r="J50" s="17" t="n"/>
-      <c r="K50" s="17" t="n"/>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="G69" s="17" t="n"/>
+      <c r="H69" s="17" t="n"/>
+      <c r="I69" s="17" t="n"/>
+      <c r="J69" s="17" t="n"/>
+      <c r="K69" s="17" t="n"/>
+    </row>
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n"/>
-      <c r="C52" s="20" t="n"/>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="20" t="n"/>
-      <c r="G52" s="20" t="n"/>
-      <c r="H52" s="20" t="n"/>
-      <c r="I52" s="20" t="n"/>
-      <c r="J52" s="20" t="n"/>
-      <c r="K52" s="20" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="n"/>
+      <c r="F71" s="20" t="n"/>
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="20" t="n"/>
+      <c r="J71" s="20" t="n"/>
+      <c r="K71" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="G62:K62"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="G30:K30"/>
-    <mergeCell ref="A37:K37"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="G43:K43"/>
-    <mergeCell ref="A29:K29"/>
     <mergeCell ref="G24:K24"/>
-    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A71:K71"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
